--- a/no_match_residual/no_match_residual_2022.xlsx
+++ b/no_match_residual/no_match_residual_2022.xlsx
@@ -557,21 +557,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -772,21 +772,21 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -845,21 +845,21 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -918,21 +918,21 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -985,21 +985,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1119,21 +1119,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1186,21 +1186,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -1253,21 +1253,21 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -1328,21 +1328,21 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1403,21 +1403,21 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -1764,21 +1764,21 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1839,21 +1839,21 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1981,21 +1981,21 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2115,21 +2115,21 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -2190,21 +2190,21 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -2265,21 +2265,21 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2340,21 +2340,21 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -2488,21 +2488,21 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -2555,21 +2555,21 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -2622,21 +2622,21 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -2689,21 +2689,21 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
@@ -2756,21 +2756,21 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -2965,21 +2965,21 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -3038,21 +3038,21 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -3111,21 +3111,21 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -5062,21 +5062,21 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -5137,21 +5137,21 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -5212,21 +5212,21 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
@@ -5287,21 +5287,21 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -5362,21 +5362,21 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -5437,21 +5437,21 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -5512,21 +5512,21 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -5587,21 +5587,21 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -5662,21 +5662,21 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -5737,21 +5737,21 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -5812,21 +5812,21 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -5887,21 +5887,21 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -5962,21 +5962,21 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -6037,21 +6037,21 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -6112,21 +6112,21 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82">
@@ -6187,21 +6187,21 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -6262,21 +6262,21 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -6412,21 +6412,21 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -6487,21 +6487,21 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -6637,21 +6637,21 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -6712,21 +6712,21 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -6787,21 +6787,21 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -6862,21 +6862,21 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92">
@@ -6937,21 +6937,21 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -7012,21 +7012,21 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
@@ -7087,21 +7087,21 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
@@ -7162,21 +7162,21 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
@@ -7237,21 +7237,21 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97">
@@ -7312,21 +7312,21 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98">
@@ -7387,21 +7387,21 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -7462,21 +7462,21 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100">
@@ -7537,21 +7537,21 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -7612,21 +7612,21 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
@@ -7687,21 +7687,21 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -7762,21 +7762,21 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
@@ -7837,21 +7837,21 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105">
@@ -7912,21 +7912,21 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
@@ -7987,21 +7987,21 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107">
@@ -8062,21 +8062,21 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108">
@@ -8137,21 +8137,21 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
@@ -8212,21 +8212,21 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110">
@@ -8287,21 +8287,21 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111">
@@ -8362,21 +8362,21 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112">
@@ -8437,21 +8437,21 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113">
@@ -8512,21 +8512,21 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
@@ -8662,21 +8662,21 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116">
@@ -8737,21 +8737,21 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -8812,21 +8812,21 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118">
@@ -8887,21 +8887,21 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
@@ -8962,21 +8962,21 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120">
@@ -9037,21 +9037,21 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
@@ -9238,21 +9238,21 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">
@@ -9305,21 +9305,21 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125">
@@ -9380,21 +9380,21 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126">
@@ -9455,21 +9455,21 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127">
@@ -9530,21 +9530,21 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128">
@@ -9605,21 +9605,21 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129">
@@ -9830,21 +9830,21 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132">
@@ -9905,21 +9905,21 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133">
@@ -9978,21 +9978,21 @@
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
@@ -10051,21 +10051,21 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -13186,21 +13186,21 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -13545,21 +13545,21 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="183">
@@ -13620,21 +13620,21 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="184">
@@ -13831,21 +13831,21 @@
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="187">
@@ -13898,21 +13898,21 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="188">
@@ -13971,21 +13971,21 @@
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189">
@@ -14044,21 +14044,21 @@
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190">
@@ -14117,21 +14117,21 @@
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191">
@@ -14190,21 +14190,21 @@
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="192">
@@ -14263,21 +14263,21 @@
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="193">
@@ -14336,21 +14336,21 @@
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194">
@@ -14409,21 +14409,21 @@
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="195">
@@ -14482,21 +14482,21 @@
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="196">
@@ -14555,21 +14555,21 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197">
@@ -14628,21 +14628,21 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198">
@@ -14701,21 +14701,21 @@
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="199">
@@ -14774,21 +14774,21 @@
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200">
@@ -14847,21 +14847,21 @@
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="201">
@@ -14920,21 +14920,21 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202">
@@ -14993,21 +14993,21 @@
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
@@ -15066,21 +15066,21 @@
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204">
@@ -15139,21 +15139,21 @@
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205">
@@ -15212,21 +15212,21 @@
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="206">
@@ -15285,21 +15285,21 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207">
@@ -15358,21 +15358,21 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208">
@@ -15431,21 +15431,21 @@
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209">
@@ -16113,21 +16113,21 @@
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="219">
@@ -16178,21 +16178,21 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="220">
@@ -16251,21 +16251,21 @@
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="221">
@@ -16324,21 +16324,21 @@
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="222">
@@ -16397,21 +16397,21 @@
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223">
@@ -16470,21 +16470,21 @@
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="224">
@@ -16981,21 +16981,21 @@
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="231">
@@ -18037,21 +18037,21 @@
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247">
@@ -18110,21 +18110,21 @@
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -18183,21 +18183,21 @@
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="249">
@@ -18256,21 +18256,21 @@
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250">
@@ -18329,21 +18329,21 @@
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251">
@@ -18402,21 +18402,21 @@
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252">
@@ -18475,21 +18475,21 @@
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253">
@@ -18548,21 +18548,21 @@
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254">
@@ -18621,21 +18621,21 @@
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255">
@@ -18694,21 +18694,21 @@
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256">
@@ -18767,21 +18767,21 @@
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257">
@@ -18840,21 +18840,21 @@
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="258">
@@ -18913,21 +18913,21 @@
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259">
@@ -18986,21 +18986,21 @@
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260">
@@ -19059,21 +19059,21 @@
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261">
@@ -19132,21 +19132,21 @@
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262">
@@ -19205,21 +19205,21 @@
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263">
@@ -19278,21 +19278,21 @@
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="264">
@@ -19351,21 +19351,21 @@
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265">
@@ -19424,21 +19424,21 @@
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266">
@@ -19497,21 +19497,21 @@
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267">
@@ -19639,21 +19639,21 @@
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269">
@@ -19712,21 +19712,21 @@
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="270">
@@ -19785,21 +19785,21 @@
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="271">
@@ -20010,21 +20010,21 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274">
@@ -20085,21 +20085,21 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="275">
@@ -20160,21 +20160,21 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="276">
@@ -20377,21 +20377,21 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="279">
@@ -20444,21 +20444,21 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="280">
@@ -20519,21 +20519,21 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="281">
@@ -20594,21 +20594,21 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="282">
@@ -20669,21 +20669,21 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="283">
@@ -20744,21 +20744,21 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284">
@@ -20819,21 +20819,21 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="285">
@@ -20894,21 +20894,21 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286">
@@ -20969,21 +20969,21 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287">
@@ -21044,21 +21044,21 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="288">
@@ -21119,21 +21119,21 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="289">
@@ -21194,21 +21194,21 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="290">
@@ -21269,21 +21269,21 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="291">
@@ -21344,21 +21344,21 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="292">
@@ -21419,21 +21419,21 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="293">
@@ -21494,21 +21494,21 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="294">
@@ -21569,21 +21569,21 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="295">
@@ -21644,21 +21644,21 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="296">
@@ -21719,21 +21719,21 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="297">
@@ -21794,21 +21794,21 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="298">
@@ -21869,21 +21869,21 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="299">
@@ -21944,21 +21944,21 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="300">
@@ -22019,21 +22019,21 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="301">
@@ -22094,21 +22094,21 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="302">
@@ -22169,21 +22169,21 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303">
@@ -22244,21 +22244,21 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="304">
@@ -22319,21 +22319,21 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="305">
@@ -22394,21 +22394,21 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="306">
@@ -22469,21 +22469,21 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="307">
@@ -22544,21 +22544,21 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308">
@@ -22619,21 +22619,21 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="309">
@@ -22686,21 +22686,21 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310">
@@ -23398,21 +23398,21 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="320">
@@ -23473,21 +23473,21 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="321">
@@ -23548,21 +23548,21 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="322">
@@ -23623,21 +23623,21 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="323">
@@ -23698,21 +23698,21 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="324">
@@ -23773,21 +23773,21 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="325">
@@ -23848,21 +23848,21 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="326">
@@ -23923,21 +23923,21 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="327">
@@ -23998,21 +23998,21 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="328">
@@ -24073,21 +24073,21 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="329">
@@ -24148,21 +24148,21 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="330">
@@ -24223,21 +24223,21 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="331">
@@ -24298,21 +24298,21 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="332">
@@ -24373,21 +24373,21 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="333">
@@ -24448,21 +24448,21 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="334">
@@ -24523,21 +24523,21 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="335">
@@ -24598,21 +24598,21 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="336">
@@ -24671,21 +24671,21 @@
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="337">
@@ -24744,21 +24744,21 @@
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="338">
@@ -24817,21 +24817,21 @@
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="339">
@@ -24890,21 +24890,21 @@
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="340">
@@ -24963,21 +24963,21 @@
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="341">
@@ -25036,21 +25036,21 @@
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
